--- a/reports/Debug-purgatory-20260105/For The Day (Actual)_Budget.xlsx
+++ b/reports/Debug-purgatory-20260105/For The Day (Actual)_Budget.xlsx
@@ -19,6 +19,30 @@
     <t>Department</t>
   </si>
   <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D5820</t>
+  </si>
+  <si>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>99200</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
     <t>99150</t>
   </si>
   <si>
@@ -40,10 +64,16 @@
     <t>D8040</t>
   </si>
   <si>
-    <t>99200</t>
-  </si>
-  <si>
-    <t>D8050</t>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D4056</t>
+  </si>
+  <si>
+    <t>D5208</t>
+  </si>
+  <si>
+    <t>D5810</t>
   </si>
   <si>
     <t>D1010</t>
@@ -103,36 +133,6 @@
     <t>D8020</t>
   </si>
   <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D4056</t>
-  </si>
-  <si>
-    <t>D5208</t>
-  </si>
-  <si>
-    <t>D5810</t>
-  </si>
-  <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D5820</t>
-  </si>
-  <si>
-    <t>D6212</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
     <t>D1000</t>
   </si>
   <si>
@@ -160,21 +160,45 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Payroll</t>
+  </si>
+  <si>
     <t>Visits</t>
   </si>
   <si>
-    <t>Payroll</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
     <t>Amount</t>
   </si>
   <si>
     <t>DepartmentTitle</t>
   </si>
   <si>
+    <t>Grounds Maintenance</t>
+  </si>
+  <si>
+    <t>Lift Maintenance</t>
+  </si>
+  <si>
+    <t>Trail Maintenance</t>
+  </si>
+  <si>
+    <t>Functions</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Winter Season Pass Visits  - Home Resort</t>
+  </si>
+  <si>
+    <t>Risk Management</t>
+  </si>
+  <si>
     <t>Comp Tickets</t>
   </si>
   <si>
@@ -196,10 +220,16 @@
     <t>HR</t>
   </si>
   <si>
-    <t>Winter Season Pass Visits  - Home Resort</t>
-  </si>
-  <si>
-    <t>Risk Management</t>
+    <t>Snowmaking</t>
+  </si>
+  <si>
+    <t>Branded</t>
+  </si>
+  <si>
+    <t>Purgy's</t>
+  </si>
+  <si>
+    <t>Events</t>
   </si>
   <si>
     <t>Lift Operations</t>
@@ -257,36 +287,6 @@
   </si>
   <si>
     <t>Accounting</t>
-  </si>
-  <si>
-    <t>Grounds Maintenance</t>
-  </si>
-  <si>
-    <t>Snowmaking</t>
-  </si>
-  <si>
-    <t>Branded</t>
-  </si>
-  <si>
-    <t>Purgy's</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Lift Maintenance</t>
-  </si>
-  <si>
-    <t>Trail Maintenance</t>
-  </si>
-  <si>
-    <t>Functions</t>
-  </si>
-  <si>
-    <t>Purgatory</t>
-  </si>
-  <si>
-    <t>Housekeeping</t>
   </si>
   <si>
     <t>Mountain G&amp;A</t>
@@ -704,7 +704,7 @@
         <v>48</v>
       </c>
       <c r="C2" s="2">
-        <v>251.00</v>
+        <v>376.71</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>53</v>
@@ -712,44 +712,44 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C3" s="2">
-        <v>1050.93</v>
+        <v>1592.10</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C4" s="2">
-        <v>1066.11</v>
+        <v>2673.06</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C5" s="2">
-        <v>928.00</v>
+        <v>2383.56</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -757,10 +757,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2">
-        <v>4846.01</v>
+        <v>594.37</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>56</v>
@@ -771,10 +771,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2">
-        <v>321.12</v>
+        <v>33687.30</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>57</v>
@@ -782,170 +782,170 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C8" s="2">
-        <v>1260.41</v>
+        <v>1714.00</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C9" s="2">
-        <v>988.51</v>
+        <v>694.73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C10" s="2">
-        <v>1063.00</v>
+        <v>0.00</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" s="2">
-        <v>227.21</v>
+        <v>1063.00</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C12" s="2">
-        <v>4633.27</v>
+        <v>227.21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" s="2">
-        <v>906.00</v>
+        <v>251.00</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C14" s="2">
-        <v>3925.46</v>
+        <v>1050.93</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C15" s="2">
-        <v>1006.39</v>
+        <v>1066.11</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2">
-        <v>181430.42</v>
+        <v>928.00</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2">
-        <v>586.26</v>
+        <v>4846.01</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2">
-        <v>2566.18</v>
+        <v>321.12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2">
-        <v>3900.99</v>
+        <v>1260.41</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -956,7 +956,7 @@
         <v>49</v>
       </c>
       <c r="C20" s="2">
-        <v>649.76</v>
+        <v>988.51</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>67</v>
@@ -970,7 +970,7 @@
         <v>49</v>
       </c>
       <c r="C21" s="2">
-        <v>169.03</v>
+        <v>236.90</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>68</v>
@@ -978,16 +978,16 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2">
-        <v>1035.18</v>
+        <v>4379.63</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -998,7 +998,7 @@
         <v>49</v>
       </c>
       <c r="C23" s="2">
-        <v>1169.78</v>
+        <v>138.75</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>69</v>
@@ -1006,16 +1006,16 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C24" s="2">
-        <v>4519.34</v>
+        <v>2797.10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1023,10 +1023,10 @@
         <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2">
-        <v>1190.63</v>
+        <v>13490.11</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>70</v>
@@ -1034,16 +1034,16 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="2">
-        <v>1745.45</v>
+        <v>201.25</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1051,10 +1051,10 @@
         <v>19</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="2">
-        <v>1280.69</v>
+        <v>0.00</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -1062,198 +1062,198 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="2">
-        <v>1635.79</v>
+        <v>4633.27</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C29" s="2">
-        <v>849.62</v>
+        <v>906.00</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C30" s="2">
-        <v>1130.00</v>
+        <v>3925.46</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C31" s="2">
-        <v>5941.92</v>
+        <v>1006.39</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C32" s="2">
-        <v>26555.00</v>
+        <v>181430.42</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C33" s="2">
-        <v>266.97</v>
+        <v>586.26</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C34" s="2">
-        <v>659.88</v>
+        <v>2566.18</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2">
-        <v>28758.50</v>
+        <v>3900.99</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C36" s="2">
-        <v>1783.26</v>
+        <v>649.76</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="2">
-        <v>7047.16</v>
+        <v>169.03</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="2">
-        <v>2266.33</v>
+        <v>1035.18</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="2">
-        <v>2298.88</v>
+        <v>1169.78</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="2">
-        <v>321.50</v>
+        <v>4519.34</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C41" s="2">
-        <v>642.47</v>
+        <v>1190.63</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1261,10 +1261,10 @@
         <v>28</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42" s="2">
-        <v>860.16</v>
+        <v>1745.45</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>80</v>
@@ -1275,10 +1275,10 @@
         <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="2">
-        <v>376.71</v>
+        <v>1280.69</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>81</v>
@@ -1289,10 +1289,10 @@
         <v>29</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44" s="2">
-        <v>1592.10</v>
+        <v>1635.79</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>81</v>
@@ -1306,7 +1306,7 @@
         <v>49</v>
       </c>
       <c r="C45" s="2">
-        <v>236.90</v>
+        <v>849.62</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>82</v>
@@ -1320,7 +1320,7 @@
         <v>50</v>
       </c>
       <c r="C46" s="2">
-        <v>4379.63</v>
+        <v>1130.00</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>83</v>
@@ -1328,16 +1328,16 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C47" s="2">
-        <v>138.75</v>
+        <v>5941.92</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1345,10 +1345,10 @@
         <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" s="2">
-        <v>2797.10</v>
+        <v>26555.00</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>84</v>
@@ -1356,16 +1356,16 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" s="2">
-        <v>13490.11</v>
+        <v>266.97</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1373,10 +1373,10 @@
         <v>33</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="2">
-        <v>201.25</v>
+        <v>659.88</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>85</v>
@@ -1384,16 +1384,16 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C51" s="2">
-        <v>0.00</v>
+        <v>28758.50</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1404,7 +1404,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="2">
-        <v>2673.06</v>
+        <v>1783.26</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>86</v>
@@ -1415,10 +1415,10 @@
         <v>35</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53" s="2">
-        <v>2383.56</v>
+        <v>7047.16</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>87</v>
@@ -1426,58 +1426,58 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C54" s="2">
-        <v>594.37</v>
+        <v>2266.33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C55" s="2">
-        <v>33687.30</v>
+        <v>2298.88</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C56" s="2">
-        <v>1714.00</v>
+        <v>321.50</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C57" s="2">
-        <v>694.73</v>
+        <v>642.47</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1485,10 +1485,10 @@
         <v>38</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C58" s="2">
-        <v>0.00</v>
+        <v>860.16</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>90</v>
@@ -1527,7 +1527,7 @@
         <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C61" s="2">
         <v>12200.43</v>
@@ -1555,7 +1555,7 @@
         <v>41</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C63" s="2">
         <v>1100.65</v>
@@ -1583,7 +1583,7 @@
         <v>42</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C65" s="2">
         <v>720.12</v>
@@ -1611,7 +1611,7 @@
         <v>43</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C67" s="2">
         <v>1147.10</v>
@@ -1639,7 +1639,7 @@
         <v>44</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C69" s="2">
         <v>221.25</v>
@@ -1667,7 +1667,7 @@
         <v>45</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C71" s="2">
         <v>863.28</v>
@@ -1681,7 +1681,7 @@
         <v>46</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C72" s="2">
         <v>0.00</v>
